--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,52 +1273,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Adoption Data Specialist (mid-career)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0211cc478db702bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Software Engineer Full Stack</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
+          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II - Machine Learning Platform</t>
+          <t>AI Adoption Data Specialist (mid-career)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0211cc478db702bd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect III</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>University of North Florida</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Warehouse Architect III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of North Florida</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
+          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,24 +1956,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71ab05047da43be</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff41688a8024c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a71ab05047da43be</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff41688a8024c3f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hunt Electric Corporation</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III - Kubernetes</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Agentic AI FDE | USA | FTE Only</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Hunt Electric Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a599c138b53329f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dev Ops &amp; Cloud Engineer</t>
+          <t>Software Engineer III - Kubernetes</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8987de444a785df</t>
+          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Agentic AI FDE | USA | FTE Only</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
+          <t>https://www.indeed.com/viewjob?jk=a599c138b53329f5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Dev Ops &amp; Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
+          <t>https://www.indeed.com/viewjob?jk=e8987de444a785df</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HealthEquity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
+          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bc362de25dc1c7</t>
+          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>HealthEquity Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61795e8b4c6bd374</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4387c130a5f162f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bc362de25dc1c7</t>
         </is>
       </c>
     </row>
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad2f0865c9b1aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=61795e8b4c6bd374</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,87 +2586,87 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=4387c130a5f162f6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c53e56424d589bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ad2f0865c9b1aca2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6720f0090cb9df</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
@@ -2678,20 +2678,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=0c53e56424d589bd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6720f0090cb9df</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Real-Time &amp; Distributed Systems (GCP)</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Flume, Spark, Scala, Kafka, NoSQL, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0c4d5bc1c777a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Data Engineer – Real-Time &amp; Distributed Systems (GCP)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Flume, Spark, Scala, Kafka, NoSQL, Airflow, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0c4d5bc1c777a9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Python/SQL</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Software Engineer III - PySpark/Python/SQL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a426d19d65d85313</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79706193aa20898</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
+          <t>https://www.indeed.com/viewjob?jk=a426d19d65d85313</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=e79706193aa20898</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SAP ABAP Developer IS-U</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EffOne Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,15 +3496,85 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer IS-U</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EffOne Software</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cdbce515fb3d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41ded37aa27d304</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=86cdbce515fb3d0a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=e41ded37aa27d304</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
@@ -2708,35 +2708,35 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6720f0090cb9df</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Real-Time &amp; Distributed Systems (GCP)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Flume, Spark, Scala, Kafka, NoSQL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0c4d5bc1c777a9</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Software Engineer III - PySpark/Python/SQL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Data Engineer – Real-Time &amp; Distributed Systems (GCP)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Flume, Spark, Scala, Kafka, NoSQL, Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0c4d5bc1c777a9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=a426d19d65d85313</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Python/SQL</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
+          <t>https://www.indeed.com/viewjob?jk=e79706193aa20898</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a426d19d65d85313</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79706193aa20898</t>
+          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>SAP ABAP Developer IS-U</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EffOne Software</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3540,41 +3540,6 @@
         </is>
       </c>
       <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud ETL Software Engineer III</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Gentiva</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, HBase, Spark, PySpark, Scala, Oracle</t>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9469b5a1b4afeae2</t>
+          <t>https://www.indeed.com/viewjob?jk=4979b99382efe90b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer-Data Engineering, Machine Learning (ML)</t>
+          <t>Cloud ETL Software Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, HBase, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78a42f096a1cab8</t>
+          <t>https://www.indeed.com/viewjob?jk=9469b5a1b4afeae2</t>
         </is>
       </c>
     </row>
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc9e6baf21076a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c78a42f096a1cab8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer-Data Engineering, Machine Learning (ML)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc414753b20eb42</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc9e6baf21076a2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Control-M Developer with Data Engineering Experience</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tms Llc</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa6d1bded85d651</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc414753b20eb42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-5</t>
+          <t>Control-M Developer with Data Engineering Experience</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tms Llc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Lambda, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
+          <t>https://www.indeed.com/viewjob?jk=baa6d1bded85d651</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Developer/Data Engineer</t>
+          <t>Sr. Qlik Data Engineer-5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,29 +696,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, Mulesoft &amp; API Development (Remote)</t>
+          <t>Developer/Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd96e6c39f5d33ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Enterprise Data</t>
+          <t>Senior Software Engineer - Java, Microservices, Mulesoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arrowstreet Capital LP</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4f624d2aeecec4</t>
+          <t>https://www.indeed.com/viewjob?jk=bd96e6c39f5d33ee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer, Enterprise Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Arrowstreet Capital LP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4f624d2aeecec4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cdbce515fb3d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41ded37aa27d304</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -1068,20 +1068,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
+          <t>https://www.indeed.com/viewjob?jk=86cdbce515fb3d0a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=e41ded37aa27d304</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
+          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,112 +1291,112 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Adoption Data Specialist (mid-career)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0211cc478db702bd</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II - Machine Learning Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect III</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>University of North Florida</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Software Engineer Full Stack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Adoption Data Specialist (mid-career)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=0211cc478db702bd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer II - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
+          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Data Warehouse Architect III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>University of North Florida</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
+          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,102 +1931,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71ab05047da43be</t>
+          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff41688a8024c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software AI Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hunt Electric Corporation</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Kubernetes</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Agentic AI FDE | USA | FTE Only</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a599c138b53329f5</t>
+          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Dev Ops &amp; Cloud Engineer</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8987de444a785df</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff41688a8024c3f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HealthEquity Inc.</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bc362de25dc1c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61795e8b4c6bd374</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Hunt Electric Corporation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4387c130a5f162f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer III - Kubernetes</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad2f0865c9b1aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Agentic AI FDE | USA | FTE Only</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a599c138b53329f5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Dev Ops &amp; Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c53e56424d589bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e8987de444a785df</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HealthEquity Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Python/SQL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,59 +3016,59 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=0c53e56424d589bd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Real-Time &amp; Distributed Systems (GCP)</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Flume, Spark, Scala, Kafka, NoSQL, Airflow, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0c4d5bc1c777a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a426d19d65d85313</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3151,29 +3151,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79706193aa20898</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Software Engineer III - PySpark/Python/SQL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Senior Data Engineer – Real-Time &amp; Distributed Systems (GCP)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Flume, Spark, Scala, Kafka, NoSQL, Airflow, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0c4d5bc1c777a9</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=a426d19d65d85313</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+          <t>https://www.indeed.com/viewjob?jk=e79706193aa20898</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SAP ABAP Developer IS-U</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EffOne Software</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,15 +3531,400 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Advanced AI Engineer (Generative AI)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ＡＮＧＥＬ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Authority Brands</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Breeze Airways</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer IS-U</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EffOne Software</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
+          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
+          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Adoption Data Specialist (mid-career)</t>
+          <t>Software Engineer Full Stack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,59 +1676,59 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0211cc478db702bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>AI Adoption Data Specialist (mid-career)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
+          <t>https://www.indeed.com/viewjob?jk=0211cc478db702bd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II - Machine Learning Platform</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect III</t>
+          <t>Software Engineer II - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>University of North Florida</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
+          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Warehouse Architect III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of North Florida</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
+          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer - Fullstack</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2276,29 +2276,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Software AI Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
         </is>
       </c>
     </row>
@@ -2416,64 +2416,64 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff41688a8024c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff41688a8024c3f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hunt Electric Corporation</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III - Kubernetes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hunt Electric Corporation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Agentic AI FDE | USA | FTE Only</t>
+          <t>Software Engineer III - Kubernetes</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a599c138b53329f5</t>
+          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dev Ops &amp; Cloud Engineer</t>
+          <t>Agentic AI FDE | USA | FTE Only</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8987de444a785df</t>
+          <t>https://www.indeed.com/viewjob?jk=a599c138b53329f5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Dev Ops &amp; Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RCH Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8987de444a785df</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HealthEquity Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>HealthEquity Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c53e56424d589bd</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Real-Time &amp; Distributed Systems (GCP)</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Flume, Spark, Scala, Kafka, NoSQL, Airflow, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0c4d5bc1c777a9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a426d19d65d85313</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79706193aa20898</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Sr. Site Reliability Engineer, Observability</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>SAP ABAP Developer IS-U</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EffOne Software</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3855,76 +3855,6 @@
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,12 +893,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=86cdbce515fb3d0a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=e41ded37aa27d304</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cdbce515fb3d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41ded37aa27d304</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
+          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
+          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
+          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Adoption Data Specialist (mid-career)</t>
+          <t>Software Engineer Full Stack</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,59 +1711,59 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0211cc478db702bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>AI Adoption Data Specialist (mid-career)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
+          <t>https://www.indeed.com/viewjob?jk=0211cc478db702bd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II - Machine Learning Platform</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect III</t>
+          <t>Software Engineer II - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>University of North Florida</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
+          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Warehouse Architect III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of North Florida</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer - Fullstack</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Senior Software AI Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
@@ -2451,37 +2451,37 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff41688a8024c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hunt Electric Corporation</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Agentic AI FDE | USA | FTE Only</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a599c138b53329f5</t>
+          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dev Ops &amp; Cloud Engineer</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RCH Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8987de444a785df</t>
+          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>HealthEquity Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HealthEquity Inc.</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Python/SQL</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Software Engineer III - PySpark/Python/SQL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, Observability</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Site Reliability Engineer, Observability</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
@@ -3857,6 +3857,41 @@
       <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Breeze Airways</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,12 +893,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cdbce515fb3d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41ded37aa27d304</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=86cdbce515fb3d0a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=e41ded37aa27d304</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
         </is>
       </c>
     </row>
@@ -1728,42 +1728,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Adoption Data Specialist (mid-career)</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0211cc478db702bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Software Engineer II - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
+          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II - Machine Learning Platform</t>
+          <t>Data Warehouse Architect III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>University of North Florida</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect III</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>University of North Florida</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
+          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer - Fullstack</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Senior Software AI Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,24 +2376,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
         </is>
       </c>
     </row>
@@ -2463,25 +2463,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer III - Kubernetes</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III - Kubernetes</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
+          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
         </is>
       </c>
     </row>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
+          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>HealthEquity Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HealthEquity Inc.</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Systems Analyst 2 (529601635)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5d3ad4cb950114</t>
         </is>
       </c>
     </row>
@@ -3058,12 +3058,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Software Engineer III - PySpark/Python/SQL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Python/SQL</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, Observability</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Site Reliability Engineer, Observability</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SAP ABAP Developer IS-U</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EffOne Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,42 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer IS-U</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EffOne Software</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, Mulesoft &amp; API Development (Remote)</t>
+          <t>Senior Platform Engineer, Enterprise Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Arrowstreet Capital LP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd96e6c39f5d33ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4f624d2aeecec4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Enterprise Data</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arrowstreet Capital LP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4f624d2aeecec4</t>
+          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
+          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,94 +1126,94 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cdbce515fb3d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41ded37aa27d304</t>
+          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,269 +1231,269 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cec3dfb04a086f</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dad972ad202e2e81</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9626985445d89a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
+          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,77 +1501,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Warehouse Architect III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>University of North Florida</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Distinguished Architect, Data and AI Integration</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff1219e8f32a9880</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
+          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II - Machine Learning Platform</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect III</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>University of North Florida</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
+          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
+          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Senior Software AI Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,77 +2271,77 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer - Fullstack</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Software Engineer III - Kubernetes</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III - Kubernetes</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HealthEquity Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Systems Analyst 2 (529601635)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HealthEquity Inc.</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5d3ad4cb950114</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=3acc87aee1bc1fbc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Township of Liberty, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=adda1ac27c2224d4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd98c9d61e607e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Systems Analyst 2 (529601635)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miamisburg, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5d3ad4cb950114</t>
+          <t>https://www.indeed.com/viewjob?jk=060b9fc9185471ea</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=d960d787222d1f56</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Founding Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=b480c210788d0b19</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/Python/SQL</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, Observability</t>
+          <t>Software Engineer III - PySpark/Python/SQL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Site Reliability Engineer, Observability</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SAP ABAP Developer IS-U</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EffOne Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,87 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer IS-U</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EffOne Software</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Breeze Airways</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud ETL Software Engineer III</t>
+          <t>Software Engineer-Data Engineering, Machine Learning (ML)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, HBase, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9469b5a1b4afeae2</t>
+          <t>https://www.indeed.com/viewjob?jk=c78a42f096a1cab8</t>
         </is>
       </c>
     </row>
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78a42f096a1cab8</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc9e6baf21076a2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer-Data Engineering, Machine Learning (ML)</t>
+          <t>Control-M Developer with Data Engineering Experience</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tms Llc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Lambda, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,137 +601,137 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc9e6baf21076a2</t>
+          <t>https://www.indeed.com/viewjob?jk=baa6d1bded85d651</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Qlik Data Engineer-5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc414753b20eb42</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Control-M Developer with Data Engineering Experience</t>
+          <t>Developer/Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tms Llc</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa6d1bded85d651</t>
+          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Developer/Data Engineer</t>
+          <t>Senior Platform Engineer, Enterprise Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Arrowstreet Capital LP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4f624d2aeecec4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Enterprise Data</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arrowstreet Capital LP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4f624d2aeecec4</t>
+          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
+          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,112 +1151,112 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
+          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0eec7b0f8281636</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II - Machine Learning Platform</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b06323be0aac0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect III</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>University of North Florida</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Distinguished Architect, Data and AI Integration</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff1219e8f32a9880</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,172 +2071,172 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer - Fullstack</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, Spark, PySpark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcb01bac518b058</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Kubernetes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, PostgreSQL, Splunk, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=becd36649959308a</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2477,11 +2477,11 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2512,11 +2512,11 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HealthEquity Inc.</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, SQL Server, MongoDB, Splunk, Azure DevOps</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd62dce3d50b914</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Systems Analyst 2 (529601635)</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5d3ad4cb950114</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acc87aee1bc1fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Township of Liberty, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adda1ac27c2224d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd98c9d61e607e</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miamisburg, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060b9fc9185471ea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,952 +3051,42 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d960d787222d1f56</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>SAP ABAP Developer IS-U</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>EffOne Software</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Founding Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>SentiLink</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b480c210788d0b19</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Driven Brands</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Teradata Developer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>UJET.cx</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Oran Inc</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Gurobi Optimization</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Data Ops Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>DHL</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Plantation, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>jamf</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>LPL Financial</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineer III - PySpark/Python/SQL</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9c1e60852a6c53</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr. Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>South Florida Community Care Network</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer, Observability</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>ＡＮＧＥＬ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Provo, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=823a1663055adb51</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Authority Brands</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Breeze Airways</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,35 +713,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Enterprise Data</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arrowstreet Capital LP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4f624d2aeecec4</t>
+          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
+          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>Caloptima</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
+          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,64 +2271,64 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>SAP ABAP Developer IS-U</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EffOne Software</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3050,41 +3050,6 @@
         </is>
       </c>
       <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Operations Engineer &amp; Analyst (Data Warehouse Programmer/Analyst)</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Caloptima</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,77 +1081,77 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252eb9f16b996c65</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,52 +1291,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1681,29 +1681,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,69 +2236,69 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,77 +1046,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb7d99af38ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a290f28a657ac35c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,54 +2211,54 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>SAP ABAP Developer IS-U</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EffOne Software</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2980,76 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Hunt Electric Corporation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,52 +2166,52 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SAP ABAP Developer IS-U</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EffOne Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,15 +2971,50 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer IS-U</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>EffOne Software</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -1238,52 +1238,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Proactive Logic Consulting Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821bd0e6e8616ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hunt Electric Corporation</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Hunt Electric Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbaed140e7cad9c</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack (Python, AWS, Glue, PySpark)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, PySpark, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5abd57a4f3ec3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>SAP ABAP Developer IS-U</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EffOne Software</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2980,41 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Control-M Developer with Data Engineering Experience</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tms Llc</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa6d1bded85d651</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc414753b20eb42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-5</t>
+          <t>Control-M Developer with Data Engineering Experience</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tms Llc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Lambda, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
+          <t>https://www.indeed.com/viewjob?jk=baa6d1bded85d651</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Developer/Data Engineer</t>
+          <t>Sr. Qlik Data Engineer-5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,77 +661,77 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer/Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
+          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
+          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,77 +1126,77 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Proactive Logic Consulting Inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,137 +1301,137 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Proactive Logic Consulting Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer Full Stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Data Warehouse Architect III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>University of North Florida</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,137 +1616,137 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>ECP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hunt Electric Corporation</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,137 +1896,137 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Software AI Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
@@ -2223,30 +2223,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
@@ -2258,55 +2258,55 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>Hunt Electric Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Systems Analyst 2 (529601635)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5d3ad4cb950114</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Fredericksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=3acc87aee1bc1fbc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Township of Liberty, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=adda1ac27c2224d4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd98c9d61e607e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miamisburg, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=060b9fc9185471ea</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,94 +2806,94 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d960d787222d1f56</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SAP ABAP Developer IS-U</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EffOne Software</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,15 +2971,715 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UJET.cx</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Advanced AI Engineer (Generative AI)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Oran Inc</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Gurobi Optimization</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Plantation, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>South Florida Community Care Network</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer, Observability</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Authority Brands</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Breeze Airways</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer IS-U</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EffOne Software</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,165 +573,165 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Qlik Data Engineer-5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc414753b20eb42</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Control-M Developer with Data Engineering Experience</t>
+          <t>Developer/Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tms Llc</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Databricks, GCP, BigQuery, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa6d1bded85d651</t>
+          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Developer/Data Engineer</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
+          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,137 +986,137 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
+          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,77 +1126,77 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Proactive Logic Consulting Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,137 +1301,137 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Proactive Logic Consulting Inc</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3324a6eac8825857</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect III</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>University of North Florida</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f996a8327315e55</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,137 +1616,137 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98807f643181f187</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ECP</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1745da350b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer – Identity Shield &amp; Consumer Fraud - Shield</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1496bf62962757c0</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Hunt Electric Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,137 +1896,137 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer - Fullstack</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eec46adb7daf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
@@ -2223,30 +2223,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
@@ -2258,55 +2258,55 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hunt Electric Corporation</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Systems Analyst 2 (529601635)</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5d3ad4cb950114</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acc87aee1bc1fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>South Florida Community Care Network</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Township of Liberty, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adda1ac27c2224d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bd98c9d61e607e</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miamisburg, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060b9fc9185471ea</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,94 +2806,94 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d960d787222d1f56</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>SAP ABAP Developer IS-U</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EffOne Software</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2980,706 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>UJET.cx</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Oran Inc</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Gurobi Optimization</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Ops Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>DHL</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Plantation, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>jamf</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>LPL Financial</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Sr. Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>South Florida Community Care Network</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer, Observability</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Authority Brands</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Breeze Airways</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,35 +678,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Senior Platform Engineer, Enterprise Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Arrowstreet Capital LP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4f624d2aeecec4</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
+          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
+          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Proactive Logic Consulting Inc</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Proactive Logic Consulting Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1611,29 +1611,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Modeler - Senior - Consulting - Miami/South Florida</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6406a6217d77067e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>South Florida Community Care Network</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, SQL Server, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfc0fd8e53ba873</t>
+          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>SAP ABAP Developer IS-U</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EffOne Software</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2945,41 +2945,6 @@
         </is>
       </c>
       <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer – Kafka, Snowflake, Google Dataflow</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b91cda9ef9060b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1611,29 +1611,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,69 +1641,69 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Hunt Electric Corporation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hunt Electric Corporation</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,69 +2166,69 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Backend Data Engineer - Reference Data (AWS)</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d78cc9cf102ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91fd4a988a79b3be</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>SAP ABAP Developer IS-U</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>EffOne Software</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,120 +2831,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Scala, Snowflake, Kimball, ELT, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28328c6440c6759e</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93230a817c21d390</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,122 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer IS-U</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>EffOne Software</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=280a9a73ca5aee29</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Darwill, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0765c167a722af00</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hunt Electric Corporation</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9c9040666ecad3</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Advanced AI Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,85 +2656,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,165 +503,165 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer-Data Engineering, Machine Learning (ML)</t>
+          <t>Sr. Qlik Data Engineer-5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78a42f096a1cab8</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer-Data Engineering, Machine Learning (ML)</t>
+          <t>Developer/Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc9e6baf21076a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Developer/Data Engineer</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
+          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Enterprise Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arrowstreet Capital LP</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4f624d2aeecec4</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,277 +916,277 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36d84b113f1f344f</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7b49ff2a7c8e26</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Proactive Logic Consulting Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Darwill, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3140b12701cf34</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb7c2eb9c514fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,102 +1826,102 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
@@ -1943,20 +1943,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2206,29 +2206,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer (Generative AI)</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2280,391 +2280,6 @@
         </is>
       </c>
       <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a32e71c90b7de7dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Oran Inc</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Gurobi Optimization</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Data Ops Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>DHL</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Plantation, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d98e661699e736</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa4c9f6052b8eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Breeze Airways</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-5</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Storable</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc414753b20eb42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Developer/Data Engineer</t>
+          <t>Sr. Qlik Data Engineer-5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b25841578b7a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
         </is>
       </c>
     </row>
@@ -958,60 +958,60 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Senior Systems Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>TNT Crane &amp; Rigging</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Databricks Developer-2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Proactive Logic Consulting Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Warehouse Architect III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>University of North Florida</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,94 +1266,94 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9c7c38b976d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Sr DevOPS Engineer-5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr DevOPS Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Governance Senior</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AST SpaceMobile</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
+          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ascension</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
+          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Driven Brands</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,89 +1931,89 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UJET.cx</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
+          <t>Systems Analyst 2 (529601635)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5d3ad4cb950114</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>UJET.cx</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
@@ -2271,15 +2271,260 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Plantation, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer, Observability</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Breeze Airways</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Migration Analyst</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
         </is>

--- a/results/job_matches_2026-02-21.xlsx
+++ b/results/job_matches_2026-02-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storable</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc414753b20eb42</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Qlik Data Engineer-5</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb9cae99211087</t>
+          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer -Big Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed48e228bf802be</t>
+          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e579feba72cf8610</t>
+          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer -Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, API Gateway, ECS, Hadoop, HDFS, MapReduce, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faece3b1d96f1a60</t>
+          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Climate First Bank</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
+          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076aeec9919fbfac</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab10a470f7a528e</t>
+          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Climate First Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19759311cb071391</t>
+          <t>https://www.indeed.com/viewjob?jk=51be9b8186852596</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect - Databricks</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c8e11f3b1f4098</t>
+          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813ed987c3044405</t>
+          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technical Architect - Databricks</t>
+          <t>Data Scientist / Data Science Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2439e6093084e24</t>
+          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Snowflake, MongoDB, DynamoDB, NoSQL, Star Schema, CI/CD</t>
+          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aedb77097be25e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Systems Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TNT Crane &amp; Rigging</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>La Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Dataflow, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcccbaa186490e37</t>
+          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Science Specialist</t>
+          <t>Senior Software AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Southern New Hampshire University</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91cd87d39ed00187</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Software Engineer (hybrid)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11ce56e07f4ef5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-2</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Best Egg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009f82f020c79472</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Engineers &amp; Constructors International</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>La Mesa, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edff2a9913d6e416</t>
+          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Sr. Integration Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ca5d0cbf6168e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric &amp; Power BI Consultant (AI-Forward) — Healthcare Data &amp; Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Proactive Logic Consulting Inc</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, Data Modeling, Dimensional Modeling</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c62c91a087c2799</t>
+          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect III</t>
+          <t>Dev Ops and Cloud Engineer, Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>University of North Florida</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92df448e2bd9201</t>
+          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>ELT Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, DynamoDB, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2b427895c42617</t>
+          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (hybrid)</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5227f1e48c9e496</t>
+          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software AI Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Southern New Hampshire University</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, Scala, Oracle, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf894cd20490ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Engineers &amp; Constructors International</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d1e56137c584a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Senior Machine Learning Engineer, Risk Modeling</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Best Egg</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff6ad916136713c</t>
+          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer-5</t>
+          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bdabd3815814e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr DevOPS Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Blob Storage, Snowflake, dbt</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,102 +1476,102 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249ea09c5d6dec62</t>
+          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Integration Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Hadoop, Spark, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf85a045c6e50084</t>
+          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ELT Engineer</t>
+          <t>Data Governance Senior</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>AST SpaceMobile</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82219bd7e68fd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Ascension</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587df161b94e20e7</t>
+          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dev Ops and Cloud Engineer, Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Driven Brands</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73c18f9abaa746c</t>
+          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a8a2a71007930a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d1ac103ab878235</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2749ecb9f8a0dc09</t>
+          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Risk Modeling</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, PySpark, Snowflake, MySQL, Tableau, MLflow</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,777 +1756,42 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f57fcb65df08a3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55eccc124ebf309a</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Application Support Analyst</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58fa4e68f1d77423</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Abbott</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44aa0d70d66a42cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Data Engineer - Cloud Data Platform (Snowflake &amp; dbt)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>AssistRx</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Maitland, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b78039922ffb238e</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Grainger</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca71348ca74ae1ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Data Governance Senior</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>AST SpaceMobile</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Lanham, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=448a79b744e2442c</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Systems Analyst 2 (529601635)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>LMG Technology Services LLC</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f5d3ad4cb950114</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Ascension</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11c257b267f7ca14</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89cedea96b8947cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Driven Brands</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Scala, Snowflake, SQL Server, MySQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=039063e25cce7591</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Teradata Developer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd891a0355d45f2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>UJET.cx</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1967303414b6d426</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer- Snowflake - USC/GC (federal client)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Oran Inc</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9af366e1c74efef</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; Analytics Engineer (USA - Remote)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Gurobi Optimization</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1e649bb5821eba</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52726d30e21dbe2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c11394b3921d3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Data Ops Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>DHL</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Plantation, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20e4b2ce9d36c600</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer, Observability</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f51bf904dca976</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Breeze Airways</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d767420f2a9716f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=499d0adf0e3292cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe55e725dce35d82</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Data Migration Analyst</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39a2d32f7b8310</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b32f6f53279a94</t>
         </is>
       </c>
     </row>
